--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488065_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488065_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>J. MOLINA VERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9464</v>
+        <v>0.819</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5072</v>
+        <v>-0.1877</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5607</v>
+        <v>1.0067</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1423</v>
+        <v>1.6073</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.3003</v>
+        <v>1.064</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1579</v>
+        <v>0.5433</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2131</v>
+        <v>0.9282</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2372</v>
+        <v>0.9282</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4503</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3554</v>
+        <v>0.6791</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0631</v>
+        <v>0.1358</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7076</v>
+        <v>0.5433</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2959</v>
+        <v>0.0046</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0097</v>
+        <v>-0.1248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2861</v>
+        <v>0.1294</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MOLINA VERA</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8471</v>
+        <v>0.7261</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1877</v>
+        <v>1.2869</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0348</v>
+        <v>-0.5607</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6073</v>
+        <v>-0.1423</v>
       </c>
       <c r="H4" t="n">
-        <v>1.064</v>
+        <v>-2.3003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5433</v>
+        <v>2.1579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9282</v>
+        <v>0.2131</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9282</v>
+        <v>-1.2372</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4503</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6791</v>
+        <v>-0.3554</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1358</v>
+        <v>-1.0631</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5433</v>
+        <v>0.7076</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0326</v>
+        <v>1.0756</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1248</v>
+        <v>0.7894</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1574</v>
+        <v>0.2861</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4562</v>
+        <v>0.2172</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4639</v>
+        <v>-0.8714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9202</v>
+        <v>1.0886</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0122</v>
@@ -844,13 +844,13 @@
         <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4684</v>
+        <v>0.2294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4295</v>
+        <v>0.0221</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0389</v>
+        <v>0.2074</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2068</v>
+        <v>-0.6943</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9836</v>
+        <v>-2.1623</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7768</v>
+        <v>1.4679</v>
       </c>
       <c r="G6" t="n">
         <v>1.9937</v>
@@ -922,13 +922,13 @@
         <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8145</v>
+        <v>1.327</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4733</v>
+        <v>0.348</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2878</v>
+        <v>0.979</v>
       </c>
       <c r="V6" t="n">
         <v>0.9405</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2941</v>
+        <v>-1.3919</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5506</v>
+        <v>-0.1991</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7436</v>
+        <v>-1.1928</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6514</v>
@@ -1000,13 +1000,13 @@
         <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3156</v>
+        <v>1.2178</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4554</v>
+        <v>0.8069</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8602</v>
+        <v>0.4109</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1476</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8669</v>
+        <v>-1.5008</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9912</v>
+        <v>-1.9059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1243</v>
+        <v>0.4051</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4323</v>
@@ -1078,13 +1078,13 @@
         <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7635999999999999</v>
+        <v>1.1297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1324</v>
+        <v>0.2177</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6312</v>
+        <v>0.912</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1413</v>
+        <v>-2.3098</v>
       </c>
       <c r="E9" t="n">
         <v>-2.1874</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0461</v>
+        <v>-0.1224</v>
       </c>
       <c r="G9" t="n">
         <v>-0.659</v>
@@ -1156,13 +1156,13 @@
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>0.251</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3758</v>
+        <v>0.2074</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3264</v>
+        <v>-2.4438</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2338</v>
+        <v>-1.2108</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0926</v>
+        <v>-1.233</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3024</v>
@@ -1234,13 +1234,13 @@
         <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8462</v>
+        <v>0.7287</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0772</v>
+        <v>0.1001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7689</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7357</v>
+        <v>-2.5433</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1402</v>
+        <v>-0.9759</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5955</v>
+        <v>-1.5674</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3044</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6383</v>
+        <v>-0.446</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2496</v>
+        <v>-0.0853</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3888</v>
+        <v>-0.3607</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.404</v>
+        <v>-3.952</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7305</v>
+        <v>-2.238</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6735</v>
+        <v>-1.7139</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7179</v>
+        <v>-2.4485</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1762</v>
+        <v>-0.9562</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8941</v>
+        <v>-1.4923</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4168</v>
+        <v>-0.4688</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9754</v>
+        <v>0.2427</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5586</v>
+        <v>-0.7115</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1347</v>
+        <v>-1.9796</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7993</v>
+        <v>-1.1989</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3355</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1893</v>
+        <v>-1.3876</v>
       </c>
       <c r="R12" t="n">
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.0982</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5616</v>
+        <v>-0.3816</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3139</v>
+        <v>0.2835</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4979</v>
+        <v>-3.958</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3628</v>
+        <v>-0.4249</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1351</v>
+        <v>-3.5331</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4485</v>
+        <v>-1.7179</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9562</v>
+        <v>0.1762</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4923</v>
+        <v>-1.8941</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4688</v>
+        <v>0.4168</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2427</v>
+        <v>0.9754</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7115</v>
+        <v>-0.5586</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9796</v>
+        <v>-2.1347</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1989</v>
+        <v>-0.7993</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.3355</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3876</v>
+        <v>-1.1893</v>
       </c>
       <c r="R13" t="n">
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6441</v>
+        <v>-0.4295</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5064</v>
+        <v>-0.256</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1377</v>
+        <v>-0.1735</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.3626</v>
+        <v>-8.9945</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.2258</v>
+        <v>-7.9138</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1369</v>
+        <v>-1.0807</v>
       </c>
       <c r="G14" t="n">
         <v>-7.3131</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1329</v>
+        <v>0.5011</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1172</v>
+        <v>0.1948</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2501</v>
+        <v>0.3063</v>
       </c>
       <c r="V14" t="n">
         <v>0.1962</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.378</v>
+        <v>-24.8181</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.3423</v>
+        <v>-17.7823</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.035699999999999</v>
+        <v>-7.0357</v>
       </c>
       <c r="G15" t="n">
         <v>-14.1745</v>
@@ -1609,7 +1609,7 @@
         <v>-12.0727</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.962399999999999</v>
+        <v>-8.962400000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-3.1107</v>
@@ -1624,16 +1624,16 @@
         <v>12.8843</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7628</v>
+        <v>5.3228</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.05350000000000002</v>
+        <v>1.5065</v>
       </c>
       <c r="U15" t="n">
-        <v>3.816000000000001</v>
+        <v>3.8163</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.046500000000001</v>
+        <v>-7.0465</v>
       </c>
       <c r="W15" t="n">
         <v>4.6173</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9981</v>
+        <v>6.8978</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4853</v>
+        <v>6.6703</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5128</v>
+        <v>0.2275</v>
       </c>
       <c r="G16" t="n">
         <v>2.6094</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4502</v>
+        <v>1.3499</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5492</v>
+        <v>0.7343</v>
       </c>
       <c r="U16" t="n">
-        <v>0.901</v>
+        <v>0.6156</v>
       </c>
       <c r="V16" t="n">
         <v>2.3438</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0376</v>
+        <v>6.8957</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8216</v>
+        <v>2.1272</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2161</v>
+        <v>4.7685</v>
       </c>
       <c r="G17" t="n">
         <v>4.9715</v>
@@ -1780,13 +1780,13 @@
         <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4096</v>
+        <v>-0.5516</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1855</v>
+        <v>-0.8799</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2241</v>
+        <v>0.3284</v>
       </c>
       <c r="V17" t="n">
         <v>1.8811</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6893</v>
+        <v>4.391</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1964</v>
+        <v>0.8193</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4929</v>
+        <v>3.5718</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4762</v>
+        <v>4.0745</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9169</v>
+        <v>0.2731</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4407</v>
+        <v>3.8013</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3335</v>
+        <v>3.9451</v>
       </c>
       <c r="K18" t="n">
-        <v>2.852</v>
+        <v>0.0478</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5184</v>
+        <v>3.8972</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8574</v>
+        <v>0.1294</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9351</v>
+        <v>0.2253</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9223</v>
+        <v>-0.0959</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-3.1716</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9822</v>
+        <v>3.3698</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6184</v>
+        <v>0.1183</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9839</v>
+        <v>-0.5578</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6761</v>
       </c>
       <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>0.6036</v>
       </c>
-      <c r="W18" t="n">
-        <v>0.8701</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.2666</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4683</v>
+        <v>2.9727</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0043</v>
+        <v>3.4689</v>
       </c>
       <c r="F19" t="n">
-        <v>3.464</v>
+        <v>-0.4962</v>
       </c>
       <c r="G19" t="n">
-        <v>4.0745</v>
+        <v>-1.7508</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2731</v>
+        <v>0.1087</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8013</v>
+        <v>-1.8596</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9451</v>
+        <v>0.4384</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0478</v>
+        <v>1.1098</v>
       </c>
       <c r="L19" t="n">
-        <v>3.8972</v>
+        <v>-0.6713</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1294</v>
+        <v>-2.1893</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2253</v>
+        <v>-1.001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0959</v>
+        <v>-1.1882</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1716</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>3.3698</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8044</v>
+        <v>0.3093</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3727</v>
+        <v>0.4002</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5684</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.6213</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>3.6213</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.0478</v>
+        <v>2.8711</v>
       </c>
       <c r="E20" t="n">
-        <v>3.8763</v>
+        <v>2.6871</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8286</v>
+        <v>0.184</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7508</v>
+        <v>0.4762</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1087</v>
+        <v>1.9169</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8596</v>
+        <v>-1.4407</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4384</v>
+        <v>2.3335</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1098</v>
+        <v>2.852</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6713</v>
+        <v>-0.5184</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1893</v>
+        <v>-1.8574</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.001</v>
+        <v>-0.9351</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1882</v>
+        <v>-0.9223</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3844</v>
+        <v>0.8002</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8077</v>
+        <v>0.4745</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4233</v>
+        <v>0.3257</v>
       </c>
       <c r="V20" t="n">
-        <v>3.6213</v>
+        <v>0.6036</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6213</v>
+        <v>0.8701</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3541</v>
+        <v>2.3731</v>
       </c>
       <c r="E21" t="n">
         <v>0.5575</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7966</v>
+        <v>1.8156</v>
       </c>
       <c r="G21" t="n">
         <v>0.9135</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.275</v>
+        <v>-0.2561</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1834</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0916</v>
+        <v>-0.0727</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2666</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3397</v>
+        <v>1.9052</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1821</v>
+        <v>-1.0802</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5217</v>
+        <v>2.9854</v>
       </c>
       <c r="G22" t="n">
         <v>1.1885</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4346</v>
+        <v>-0.8691</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5097</v>
+        <v>-0.046</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2751</v>
+        <v>1.6133</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1705</v>
+        <v>-3.2723</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4455</v>
+        <v>4.8857</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5253</v>
@@ -2248,13 +2248,13 @@
         <v>2.9733</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1908</v>
+        <v>-0.8525</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9946</v>
+        <v>-1.0964</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1962</v>
+        <v>0.2439</v>
       </c>
       <c r="V23" t="n">
         <v>1.2071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0678</v>
+        <v>1.282</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5893</v>
+        <v>0.6912</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4785</v>
+        <v>0.5909</v>
       </c>
       <c r="G24" t="n">
         <v>0.1662</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1968</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.9405</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8665</v>
+        <v>-1.134</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.138</v>
+        <v>-4.597</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7286</v>
+        <v>3.463</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2915</v>
+        <v>2.3423</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6535</v>
+        <v>0.6186</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9451000000000001</v>
+        <v>1.7237</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6388</v>
+        <v>-0.2729</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0404</v>
+        <v>-0.8873</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6791</v>
+        <v>0.6143</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3472</v>
+        <v>2.6153</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6132</v>
+        <v>1.5059</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.266</v>
+        <v>1.1094</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.696</v>
+        <v>-0.8728</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4992</v>
+        <v>-1.1525</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1968</v>
+        <v>0.2797</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4737</v>
+        <v>-1.8107</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4737</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0332</v>
+        <v>-1.6523</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.0044</v>
+        <v>-1.0361</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9712</v>
+        <v>-0.6162</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3423</v>
+        <v>-0.2915</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6186</v>
+        <v>0.6535</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7237</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2729</v>
+        <v>-0.6388</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.8873</v>
+        <v>0.0404</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6143</v>
+        <v>-0.6791</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6153</v>
+        <v>0.3472</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5059</v>
+        <v>0.6132</v>
       </c>
       <c r="O26" t="n">
-        <v>1.1094</v>
+        <v>-0.266</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3787</v>
+        <v>0.5947</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.772</v>
+        <v>-0.4818</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.5599</v>
+        <v>-0.3973</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.212</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.8107</v>
+        <v>-1.4737</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.8107</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>26.3781</v>
+        <v>28.4156</v>
       </c>
       <c r="E27" t="n">
-        <v>7.035699999999999</v>
+        <v>7.035899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>19.3421</v>
+        <v>21.38</v>
       </c>
       <c r="G27" t="n">
         <v>14.1745</v>
@@ -2539,7 +2539,7 @@
         <v>8.962300000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>3.110600000000001</v>
+        <v>3.1106</v>
       </c>
       <c r="M27" t="n">
         <v>2.1015</v>
@@ -2560,13 +2560,13 @@
         <v>21.8045</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.763</v>
+        <v>-1.7256</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.8162</v>
+        <v>-3.8163</v>
       </c>
       <c r="U27" t="n">
-        <v>0.05350000000000008</v>
+        <v>2.0908</v>
       </c>
       <c r="V27" t="n">
         <v>7.046399999999999</v>
